--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487840_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487840_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5906</v>
+        <v>2.8804</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0161</v>
+        <v>2.1885</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5745</v>
+        <v>0.6919</v>
       </c>
       <c r="G2" t="n">
         <v>1.5963</v>
@@ -610,13 +610,13 @@
         <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8194</v>
+        <v>-0.5296</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8358</v>
+        <v>-0.6634</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0164</v>
+        <v>0.1338</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5758</v>
+        <v>0.2175</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3674</v>
+        <v>-0.2086</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9432</v>
+        <v>0.4261</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3358</v>
+        <v>-1.6917</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1849</v>
+        <v>-0.1748</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8491</v>
+        <v>-1.5169</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2178</v>
+        <v>0.9782</v>
       </c>
       <c r="K3" t="n">
-        <v>2.434</v>
+        <v>0.3602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.882</v>
+        <v>-2.6699</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2492</v>
+        <v>-0.5349</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6328</v>
+        <v>-2.1349</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.1218</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.2029</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>3.054</v>
+        <v>0.2694</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6178</v>
+        <v>-0.1462</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4362</v>
+        <v>0.4156</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3078</v>
+        <v>1.0154</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3078</v>
+        <v>1.0154</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0149</v>
+        <v>0.2097</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4347</v>
+        <v>0.5419</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4496</v>
+        <v>-0.3322</v>
       </c>
       <c r="G4" t="n">
         <v>1.5591</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4032</v>
+        <v>-0.1786</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6277</v>
+        <v>-0.5205</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2245</v>
+        <v>0.3419</v>
       </c>
       <c r="V4" t="n">
         <v>0.07779999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2405</v>
+        <v>0.0712</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6372</v>
+        <v>-1.9032</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3967</v>
+        <v>1.9743</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6917</v>
+        <v>1.3358</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1748</v>
+        <v>2.1849</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5169</v>
+        <v>-0.8491</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9782</v>
+        <v>3.2178</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3602</v>
+        <v>2.434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.618</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6699</v>
+        <v>-1.882</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5349</v>
+        <v>-0.2492</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1349</v>
+        <v>-1.6328</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-5.2029</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1885</v>
+        <v>1.5493</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5748</v>
+        <v>0.082</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3863</v>
+        <v>1.4674</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0154</v>
+        <v>0.3078</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0154</v>
+        <v>0.3078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8171</v>
+        <v>-0.237</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7264</v>
+        <v>-1.0015</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0907</v>
+        <v>0.7645</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.4267</v>
+        <v>-1.0341</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0019</v>
+        <v>0.0215</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4248</v>
+        <v>-1.0556</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7446</v>
+        <v>0.5376</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5609</v>
+        <v>0.1727</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1837</v>
+        <v>0.3649</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6821</v>
+        <v>-1.5717</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4411</v>
+        <v>-0.1512</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2411</v>
+        <v>-1.4206</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>1.569</v>
+        <v>0.6787</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0588</v>
+        <v>-0.1447</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5102</v>
+        <v>0.8234</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5059</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1521</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0077</v>
+        <v>-1.0992</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5373</v>
+        <v>-2.0436</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5296</v>
+        <v>0.9444</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0341</v>
+        <v>-1.2582</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0215</v>
+        <v>-0.663</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0556</v>
+        <v>-0.5952</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5376</v>
+        <v>-0.4825</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1727</v>
+        <v>-0.5609</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3649</v>
+        <v>0.0784</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5717</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1512</v>
+        <v>-0.1022</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4206</v>
+        <v>-0.6735</v>
       </c>
       <c r="P7" t="n">
         <v>0.6244</v>
@@ -1000,28 +1000,28 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.092</v>
+        <v>-0.4193</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6805</v>
+        <v>-0.5205</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5885</v>
+        <v>0.1012</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5059</v>
+        <v>-0.046</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1521</v>
+        <v>-0.046</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3303</v>
+        <v>-1.5227</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.216</v>
+        <v>-0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8857</v>
+        <v>-0.5596</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2582</v>
+        <v>-1.4737</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.663</v>
+        <v>-0.5863</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5952</v>
+        <v>-0.8875</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4825</v>
+        <v>-0.6368</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5609</v>
+        <v>0.0384</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0784</v>
+        <v>-0.6752</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.8369</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1022</v>
+        <v>-0.6247</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6735</v>
+        <v>-0.2123</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6505</v>
+        <v>-0.4652</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6929</v>
+        <v>-0.3262</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0424</v>
+        <v>-0.139</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.046</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6107</v>
+        <v>-1.8132</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.963</v>
+        <v>-1.8399</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.0267</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4737</v>
+        <v>-3.4267</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5863</v>
+        <v>-1.0019</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8875</v>
+        <v>-2.4248</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6368</v>
+        <v>-0.7446</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0384</v>
+        <v>-0.5609</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6752</v>
+        <v>-0.1837</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8369</v>
+        <v>-2.6821</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6247</v>
+        <v>-0.4411</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2123</v>
+        <v>-2.2411</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5532</v>
+        <v>0.5729</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3262</v>
+        <v>-0.0547</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.227</v>
+        <v>0.6277</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4893</v>
+        <v>-3.3653</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8732</v>
+        <v>-1.808</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6161</v>
+        <v>-1.5574</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7991</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8338</v>
+        <v>-0.7098</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5219</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1051</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.247999999999999</v>
+        <v>-8.6073</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.738</v>
+        <v>-8.2441</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.51</v>
+        <v>-0.3632</v>
       </c>
       <c r="G11" t="n">
         <v>-8.1153</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6322</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7705</v>
+        <v>-0.2767</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1383</v>
+        <v>0.2851</v>
       </c>
       <c r="V11" t="n">
         <v>0.1238</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.5921</v>
+        <v>-13.2659</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.6077</v>
+        <v>-15.2815</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0156</v>
+        <v>2.0155</v>
       </c>
       <c r="G12" t="n">
         <v>-14.3076</v>
@@ -1366,7 +1366,7 @@
         <v>1.2058</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3486999999999987</v>
+        <v>0.3487000000000005</v>
       </c>
       <c r="L12" t="n">
         <v>0.8571999999999997</v>
@@ -1381,7 +1381,7 @@
         <v>-11.3687</v>
       </c>
       <c r="P12" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.6495</v>
@@ -1390,10 +1390,10 @@
         <v>16.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4501999999999998</v>
+        <v>0.7762999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.419</v>
+        <v>-3.0928</v>
       </c>
       <c r="U12" t="n">
         <v>3.8692</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.320399999999999</v>
+        <v>9.171200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2985</v>
+        <v>5.977</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0219</v>
+        <v>3.1942</v>
       </c>
       <c r="G13" t="n">
         <v>6.3538</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2153</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2838</v>
+        <v>0.4561</v>
       </c>
       <c r="V13" t="n">
         <v>2.3351</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1585</v>
+        <v>7.4355</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8277</v>
+        <v>3.4706</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3308</v>
+        <v>3.9649</v>
       </c>
       <c r="G14" t="n">
         <v>4.9184</v>
@@ -1546,13 +1546,13 @@
         <v>3.3299</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5279</v>
+        <v>-0.2509</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5658</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0379</v>
+        <v>0.672</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3538</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7605</v>
+        <v>3.5923</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6657</v>
+        <v>1.0943</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0948</v>
+        <v>2.498</v>
       </c>
       <c r="G15" t="n">
         <v>1.1486</v>
@@ -1624,13 +1624,13 @@
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7013</v>
+        <v>0.1305</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7829</v>
+        <v>-0.3543</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.4848</v>
       </c>
       <c r="V15" t="n">
         <v>2.1051</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>S. CHABI YO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.732</v>
+        <v>1.1689</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3815</v>
+        <v>-0.5888</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1135</v>
+        <v>1.7577</v>
       </c>
       <c r="G16" t="n">
-        <v>1.588</v>
+        <v>0.6574</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8508</v>
+        <v>1.0958</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7372</v>
+        <v>-0.4384</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5311</v>
+        <v>0.9555</v>
       </c>
       <c r="K16" t="n">
-        <v>1.296</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>0.2351</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0569</v>
+        <v>-0.2981</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4452</v>
+        <v>0.3755</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5021</v>
+        <v>-0.6735</v>
       </c>
       <c r="P16" t="n">
         <v>-1.0406</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1218</v>
+        <v>-2.2893</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1399</v>
+        <v>0.1546</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1645</v>
+        <v>-0.6524</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9754</v>
+        <v>0.8071</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9553</v>
+        <v>1.3975</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9553</v>
+        <v>1.3975</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CHABI YO</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.349</v>
+        <v>0.5543</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5888</v>
+        <v>-2.3459</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9378</v>
+        <v>2.9001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6574</v>
+        <v>1.588</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0958</v>
+        <v>0.8508</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4384</v>
+        <v>0.7372</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9555</v>
+        <v>1.5311</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7203000000000001</v>
+        <v>1.296</v>
       </c>
       <c r="L17" t="n">
         <v>0.2351</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2981</v>
+        <v>0.0569</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3755</v>
+        <v>-0.4452</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6735</v>
+        <v>0.5021</v>
       </c>
       <c r="P17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2893</v>
+        <v>-3.1218</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3347</v>
+        <v>0.9621</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6524</v>
+        <v>0.2001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9872</v>
+        <v>0.7621</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3975</v>
+        <v>-0.9553</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>-0.9553</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2006</v>
+        <v>0.2994</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3465</v>
+        <v>-0.1321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1458</v>
+        <v>0.4316</v>
       </c>
       <c r="G18" t="n">
         <v>1.647</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2857</v>
+        <v>0.2143</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4319</v>
+        <v>0.7177</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9376</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4282</v>
+        <v>-0.3719</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.868</v>
+        <v>-1.1895</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4398</v>
+        <v>0.8175</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8242</v>
@@ -1936,13 +1936,13 @@
         <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0796</v>
+        <v>-0.0233</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1338</v>
+        <v>-0.4553</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0542</v>
+        <v>0.4319</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3975</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3354</v>
+        <v>-2.9513</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.9642</v>
+        <v>-6.0714</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6288</v>
+        <v>3.12</v>
       </c>
       <c r="G20" t="n">
         <v>-1.591</v>
@@ -2014,13 +2014,13 @@
         <v>3.1218</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.475</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5905</v>
+        <v>-0.6976</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1155</v>
+        <v>0.6068</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0614</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.764</v>
+        <v>-3.1632</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6586</v>
+        <v>-2.2299</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1055</v>
+        <v>-0.9332</v>
       </c>
       <c r="G21" t="n">
         <v>0.4094</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0704</v>
+        <v>0.5304</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5219</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4515</v>
+        <v>0.6237</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3975</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>13.5922</v>
+        <v>15.7352</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.015699999999999</v>
+        <v>-2.015699999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>15.6077</v>
+        <v>17.7508</v>
       </c>
       <c r="G22" t="n">
         <v>14.3074</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3486</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8570000000000001</v>
+        <v>-0.857</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,16 +2170,16 @@
         <v>16.6495</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4500000000000002</v>
+        <v>1.693</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.869</v>
+        <v>-3.8691</v>
       </c>
       <c r="U22" t="n">
-        <v>3.419</v>
+        <v>5.5622</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2653999999999999</v>
+        <v>-0.2653999999999996</v>
       </c>
       <c r="W22" t="n">
         <v>2.9896</v>
